--- a/files/5-ezhenedelnyj-otchet.xlsx
+++ b/files/5-ezhenedelnyj-otchet.xlsx
@@ -450,32 +450,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="38" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Еженедельный отчёт</t>
+          <t>Еженедельный отчёт по блогу</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Клиент:</t>
+          <t>Аккаунт:</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[название клиента]</t>
+          <t>[@твой_аккаунт]</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="46" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Неделя</t>
@@ -499,37 +499,37 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Расход, ₽</t>
+          <t>Охват</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Показы</t>
+          <t>Просмотры профиля</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Клики</t>
+          <t>Сохранения</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>CTR, %</t>
+          <t>Новые подписчики</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>CPC, ₽</t>
+          <t>Заявки в директ</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Заявки</t>
+          <t>Сохранения, % от охвата</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>CPL, ₽</t>
+          <t>Подписчиков на 1000 охвата</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -545,32 +545,31 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>12000</v>
+        <v>48000</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>150000</v>
+        <v>1900</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2400</v>
-      </c>
-      <c r="E6" s="3">
-        <f>IF(C6=0,"",ROUND(D6/C6*100,2))</f>
-        <v/>
-      </c>
-      <c r="F6" s="3">
-        <f>IF(D6=0,"",ROUND(B6/D6,2))</f>
-        <v/>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>38</v>
+        <v>620</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G6" s="3">
+        <f>IF(B6=0,"",ROUND(D6/B6*100,2))</f>
+        <v/>
       </c>
       <c r="H6" s="3">
-        <f>IF(G6=0,"",ROUND(B6/G6,2))</f>
+        <f>IF(B6=0,"",ROUND(E6/B6*1000,1))</f>
         <v/>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Пример: тестировали два креатива</t>
+          <t>Пример: зашла карусель про нейросети</t>
         </is>
       </c>
     </row>
@@ -583,17 +582,14 @@
       <c r="B7" s="3" t="n"/>
       <c r="C7" s="3" t="n"/>
       <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3">
-        <f>IF(C7=0,"",ROUND(D7/C7*100,2))</f>
-        <v/>
-      </c>
-      <c r="F7" s="3">
-        <f>IF(D7=0,"",ROUND(B7/D7,2))</f>
-        <v/>
-      </c>
-      <c r="G7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3">
+        <f>IF(B7=0,"",ROUND(D7/B7*100,2))</f>
+        <v/>
+      </c>
       <c r="H7" s="3">
-        <f>IF(G7=0,"",ROUND(B7/G7,2))</f>
+        <f>IF(B7=0,"",ROUND(E7/B7*1000,1))</f>
         <v/>
       </c>
       <c r="I7" s="3" t="n"/>
@@ -607,17 +603,14 @@
       <c r="B8" s="3" t="n"/>
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3">
-        <f>IF(C8=0,"",ROUND(D8/C8*100,2))</f>
-        <v/>
-      </c>
-      <c r="F8" s="3">
-        <f>IF(D8=0,"",ROUND(B8/D8,2))</f>
-        <v/>
-      </c>
-      <c r="G8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3">
+        <f>IF(B8=0,"",ROUND(D8/B8*100,2))</f>
+        <v/>
+      </c>
       <c r="H8" s="3">
-        <f>IF(G8=0,"",ROUND(B8/G8,2))</f>
+        <f>IF(B8=0,"",ROUND(E8/B8*1000,1))</f>
         <v/>
       </c>
       <c r="I8" s="3" t="n"/>
@@ -631,17 +624,14 @@
       <c r="B9" s="3" t="n"/>
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3">
-        <f>IF(C9=0,"",ROUND(D9/C9*100,2))</f>
-        <v/>
-      </c>
-      <c r="F9" s="3">
-        <f>IF(D9=0,"",ROUND(B9/D9,2))</f>
-        <v/>
-      </c>
-      <c r="G9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3">
+        <f>IF(B9=0,"",ROUND(D9/B9*100,2))</f>
+        <v/>
+      </c>
       <c r="H9" s="3">
-        <f>IF(G9=0,"",ROUND(B9/G9,2))</f>
+        <f>IF(B9=0,"",ROUND(E9/B9*1000,1))</f>
         <v/>
       </c>
       <c r="I9" s="3" t="n"/>
@@ -655,17 +645,14 @@
       <c r="B10" s="3" t="n"/>
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3">
-        <f>IF(C10=0,"",ROUND(D10/C10*100,2))</f>
-        <v/>
-      </c>
-      <c r="F10" s="3">
-        <f>IF(D10=0,"",ROUND(B10/D10,2))</f>
-        <v/>
-      </c>
-      <c r="G10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3">
+        <f>IF(B10=0,"",ROUND(D10/B10*100,2))</f>
+        <v/>
+      </c>
       <c r="H10" s="3">
-        <f>IF(G10=0,"",ROUND(B10/G10,2))</f>
+        <f>IF(B10=0,"",ROUND(E10/B10*1000,1))</f>
         <v/>
       </c>
       <c r="I10" s="3" t="n"/>
@@ -679,17 +666,14 @@
       <c r="B11" s="3" t="n"/>
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3">
-        <f>IF(C11=0,"",ROUND(D11/C11*100,2))</f>
-        <v/>
-      </c>
-      <c r="F11" s="3">
-        <f>IF(D11=0,"",ROUND(B11/D11,2))</f>
-        <v/>
-      </c>
-      <c r="G11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3">
+        <f>IF(B11=0,"",ROUND(D11/B11*100,2))</f>
+        <v/>
+      </c>
       <c r="H11" s="3">
-        <f>IF(G11=0,"",ROUND(B11/G11,2))</f>
+        <f>IF(B11=0,"",ROUND(E11/B11*1000,1))</f>
         <v/>
       </c>
       <c r="I11" s="3" t="n"/>
@@ -713,19 +697,19 @@
         <v/>
       </c>
       <c r="E12" s="4">
-        <f>IF(C12=0,"",ROUND(D12/C12*100,2))</f>
+        <f>SUM(E6:E11)</f>
         <v/>
       </c>
       <c r="F12" s="4">
-        <f>IF(D12=0,"",ROUND(B12/D12,2))</f>
+        <f>SUM(F6:F11)</f>
         <v/>
       </c>
       <c r="G12" s="4">
-        <f>SUM(G6:G11)</f>
+        <f>IF(B12=0,"",ROUND(D12/B12*100,2))</f>
         <v/>
       </c>
       <c r="H12" s="4">
-        <f>IF(G12=0,"",ROUND(B12/G12,2))</f>
+        <f>IF(B12=0,"",ROUND(E12/B12*1000,1))</f>
         <v/>
       </c>
       <c r="I12" s="4" t="n"/>
@@ -733,7 +717,7 @@
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Что сработало:</t>
+          <t>Какие публикации зашли:</t>
         </is>
       </c>
       <c r="C14" s="3" t="n"/>
@@ -741,7 +725,7 @@
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Что не сработало:</t>
+          <t>Какие не зашли:</t>
         </is>
       </c>
       <c r="C15" s="3" t="n"/>
@@ -749,7 +733,7 @@
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Что делаем на следующей неделе:</t>
+          <t>Что делаю на следующей неделе:</t>
         </is>
       </c>
       <c r="C16" s="3" t="n"/>
